--- a/estimation/notsensor/DenseModel/Dense_1st_torch_optimized/IWALQQ_1st_correction/angle/4_fold/103.xlsx
+++ b/estimation/notsensor/DenseModel/Dense_1st_torch_optimized/IWALQQ_1st_correction/angle/4_fold/103.xlsx
@@ -426,13 +426,13 @@
         <v>-6.816187901216571</v>
       </c>
       <c r="E2">
-        <v>-15.90167968447996</v>
+        <v>-14.79788678748035</v>
       </c>
       <c r="F2">
-        <v>-2.94223939198314</v>
+        <v>-3.76974694941854</v>
       </c>
       <c r="G2">
-        <v>-13.11316132656388</v>
+        <v>-12.55463835515832</v>
       </c>
     </row>
     <row r="3" spans="1:7">
@@ -449,13 +449,13 @@
         <v>-7.115358348302817</v>
       </c>
       <c r="E3">
-        <v>-15.56650015232823</v>
+        <v>-16.82793375800886</v>
       </c>
       <c r="F3">
-        <v>-2.943442181452005</v>
+        <v>-3.458627063540296</v>
       </c>
       <c r="G3">
-        <v>-13.44557860152967</v>
+        <v>-11.84785995003237</v>
       </c>
     </row>
     <row r="4" spans="1:7">
@@ -472,13 +472,13 @@
         <v>-7.353847893781106</v>
       </c>
       <c r="E4">
-        <v>-16.8405953713343</v>
+        <v>-16.69203878151268</v>
       </c>
       <c r="F4">
-        <v>-2.819071099595687</v>
+        <v>-3.399174306673973</v>
       </c>
       <c r="G4">
-        <v>-13.14645588172757</v>
+        <v>-13.00384743031098</v>
       </c>
     </row>
     <row r="5" spans="1:7">
@@ -495,13 +495,13 @@
         <v>-7.507855939080105</v>
       </c>
       <c r="E5">
-        <v>-16.21548481931549</v>
+        <v>-17.71267531030944</v>
       </c>
       <c r="F5">
-        <v>-3.355054630433468</v>
+        <v>-3.52869369193869</v>
       </c>
       <c r="G5">
-        <v>-13.11190461870662</v>
+        <v>-11.57215202727847</v>
       </c>
     </row>
     <row r="6" spans="1:7">
@@ -518,13 +518,13 @@
         <v>-7.607873065166862</v>
       </c>
       <c r="E6">
-        <v>-16.94427025526591</v>
+        <v>-18.21712920086788</v>
       </c>
       <c r="F6">
-        <v>-2.750669489676921</v>
+        <v>-3.362697976459099</v>
       </c>
       <c r="G6">
-        <v>-12.36780231834198</v>
+        <v>-11.03349357119379</v>
       </c>
     </row>
     <row r="7" spans="1:7">
@@ -541,13 +541,13 @@
         <v>-7.679313485540234</v>
       </c>
       <c r="E7">
-        <v>-18.6369051559569</v>
+        <v>-18.53876406726267</v>
       </c>
       <c r="F7">
-        <v>-2.690738764819182</v>
+        <v>-3.602128462196866</v>
       </c>
       <c r="G7">
-        <v>-13.10317656935849</v>
+        <v>-10.9835730663884</v>
       </c>
     </row>
     <row r="8" spans="1:7">
@@ -564,13 +564,13 @@
         <v>-7.745932552863072</v>
       </c>
       <c r="E8">
-        <v>-18.56858859707719</v>
+        <v>-20.72639287631009</v>
       </c>
       <c r="F8">
-        <v>-3.119152161464225</v>
+        <v>-3.275657271609941</v>
       </c>
       <c r="G8">
-        <v>-12.87502010944406</v>
+        <v>-11.86336700312231</v>
       </c>
     </row>
     <row r="9" spans="1:7">
@@ -587,13 +587,13 @@
         <v>-7.826992298341348</v>
       </c>
       <c r="E9">
-        <v>-18.71056078569166</v>
+        <v>-19.71983990167719</v>
       </c>
       <c r="F9">
-        <v>-2.670066027914918</v>
+        <v>-2.930007718913403</v>
       </c>
       <c r="G9">
-        <v>-12.49996992275641</v>
+        <v>-11.70735476163539</v>
       </c>
     </row>
     <row r="10" spans="1:7">
@@ -610,13 +610,13 @@
         <v>-7.936053383919166</v>
       </c>
       <c r="E10">
-        <v>-19.73114297280033</v>
+        <v>-21.18594241860848</v>
       </c>
       <c r="F10">
-        <v>-2.400998213239791</v>
+        <v>-3.416112763326417</v>
       </c>
       <c r="G10">
-        <v>-12.13303419698527</v>
+        <v>-10.99908668192145</v>
       </c>
     </row>
     <row r="11" spans="1:7">
@@ -633,13 +633,13 @@
         <v>-8.07150132766551</v>
       </c>
       <c r="E11">
-        <v>-20.21399151386818</v>
+        <v>-21.18932971716622</v>
       </c>
       <c r="F11">
-        <v>-2.518659519133433</v>
+        <v>-3.346394049237199</v>
       </c>
       <c r="G11">
-        <v>-12.39812080555125</v>
+        <v>-11.23013061680819</v>
       </c>
     </row>
     <row r="12" spans="1:7">
@@ -656,13 +656,13 @@
         <v>-8.231284314192031</v>
       </c>
       <c r="E12">
-        <v>-20.88514758959699</v>
+        <v>-21.5800962677621</v>
       </c>
       <c r="F12">
-        <v>-2.35912838286529</v>
+        <v>-3.228371575155937</v>
       </c>
       <c r="G12">
-        <v>-12.24699758418791</v>
+        <v>-11.2629297075164</v>
       </c>
     </row>
     <row r="13" spans="1:7">
@@ -679,13 +679,13 @@
         <v>-8.395918202619368</v>
       </c>
       <c r="E13">
-        <v>-21.63633538646336</v>
+        <v>-22.47461026697123</v>
       </c>
       <c r="F13">
-        <v>-2.131789576106188</v>
+        <v>-1.998202078526323</v>
       </c>
       <c r="G13">
-        <v>-11.8501961797827</v>
+        <v>-10.82041432434501</v>
       </c>
     </row>
     <row r="14" spans="1:7">
@@ -702,13 +702,13 @@
         <v>-8.547060252385748</v>
       </c>
       <c r="E14">
-        <v>-22.51687904335883</v>
+        <v>-22.38309433575022</v>
       </c>
       <c r="F14">
-        <v>-1.872064917367237</v>
+        <v>-2.233801365026141</v>
       </c>
       <c r="G14">
-        <v>-12.43131692406815</v>
+        <v>-10.82839097395602</v>
       </c>
     </row>
     <row r="15" spans="1:7">
@@ -725,13 +725,13 @@
         <v>-8.662298365955406</v>
       </c>
       <c r="E15">
-        <v>-23.10020083723486</v>
+        <v>-24.16242687131807</v>
       </c>
       <c r="F15">
-        <v>-1.623116490171304</v>
+        <v>-2.357444311935398</v>
       </c>
       <c r="G15">
-        <v>-11.19018502554351</v>
+        <v>-11.00481241354268</v>
       </c>
     </row>
     <row r="16" spans="1:7">
@@ -748,13 +748,13 @@
         <v>-8.718401031004726</v>
       </c>
       <c r="E16">
-        <v>-24.8341852340899</v>
+        <v>-25.00441057203822</v>
       </c>
       <c r="F16">
-        <v>-1.341672038130949</v>
+        <v>-2.078952989686024</v>
       </c>
       <c r="G16">
-        <v>-11.05191434902851</v>
+        <v>-9.74595207493236</v>
       </c>
     </row>
     <row r="17" spans="1:7">
@@ -771,13 +771,13 @@
         <v>-8.701475565553798</v>
       </c>
       <c r="E17">
-        <v>-24.72723173497674</v>
+        <v>-26.98964829226083</v>
       </c>
       <c r="F17">
-        <v>-0.9507356395233619</v>
+        <v>-1.856474214479147</v>
       </c>
       <c r="G17">
-        <v>-10.81072487707997</v>
+        <v>-9.168325831607712</v>
       </c>
     </row>
     <row r="18" spans="1:7">
@@ -794,13 +794,13 @@
         <v>-8.596816420311804</v>
       </c>
       <c r="E18">
-        <v>-26.18908654328884</v>
+        <v>-27.57962694292814</v>
       </c>
       <c r="F18">
-        <v>-0.3264274343620837</v>
+        <v>-1.757520758010329</v>
       </c>
       <c r="G18">
-        <v>-10.16425204299505</v>
+        <v>-9.130165224871369</v>
       </c>
     </row>
     <row r="19" spans="1:7">
@@ -817,13 +817,13 @@
         <v>-8.401032935677572</v>
       </c>
       <c r="E19">
-        <v>-25.32053428556568</v>
+        <v>-28.47625573949886</v>
       </c>
       <c r="F19">
-        <v>-0.08086537310879549</v>
+        <v>-0.8998250073147072</v>
       </c>
       <c r="G19">
-        <v>-10.59020381973436</v>
+        <v>-9.093986475956932</v>
       </c>
     </row>
     <row r="20" spans="1:7">
@@ -840,13 +840,13 @@
         <v>-8.115592096541519</v>
       </c>
       <c r="E20">
-        <v>-27.9315935282263</v>
+        <v>-29.272773561182</v>
       </c>
       <c r="F20">
-        <v>-0.07931881116776882</v>
+        <v>-1.038395963189814</v>
       </c>
       <c r="G20">
-        <v>-10.88104145509887</v>
+        <v>-8.550973838862866</v>
       </c>
     </row>
     <row r="21" spans="1:7">
@@ -863,13 +863,13 @@
         <v>-7.744617282485396</v>
       </c>
       <c r="E21">
-        <v>-27.95841567977374</v>
+        <v>-27.76785749353097</v>
       </c>
       <c r="F21">
-        <v>0.327853588534689</v>
+        <v>-1.172946852059135</v>
       </c>
       <c r="G21">
-        <v>-9.817456455155778</v>
+        <v>-8.274035458024173</v>
       </c>
     </row>
     <row r="22" spans="1:7">
@@ -886,13 +886,13 @@
         <v>-7.30444571762876</v>
       </c>
       <c r="E22">
-        <v>-28.35209856763056</v>
+        <v>-30.16564598856336</v>
       </c>
       <c r="F22">
-        <v>0.4222328002052478</v>
+        <v>-0.1983999387898089</v>
       </c>
       <c r="G22">
-        <v>-10.05758609254062</v>
+        <v>-8.434392036855796</v>
       </c>
     </row>
     <row r="23" spans="1:7">
@@ -909,13 +909,13 @@
         <v>-6.809416259726873</v>
       </c>
       <c r="E23">
-        <v>-29.68266838598629</v>
+        <v>-30.91023579880055</v>
       </c>
       <c r="F23">
-        <v>0.3873941523457091</v>
+        <v>-0.06118419198568203</v>
       </c>
       <c r="G23">
-        <v>-9.283457333685508</v>
+        <v>-7.970499495224621</v>
       </c>
     </row>
     <row r="24" spans="1:7">
@@ -932,13 +932,13 @@
         <v>-6.28272176071658</v>
       </c>
       <c r="E24">
-        <v>-29.73052529929935</v>
+        <v>-30.93886028300303</v>
       </c>
       <c r="F24">
-        <v>1.013597662124593</v>
+        <v>0.2442183020784397</v>
       </c>
       <c r="G24">
-        <v>-10.01720738003009</v>
+        <v>-8.526673111993619</v>
       </c>
     </row>
     <row r="25" spans="1:7">
@@ -955,13 +955,13 @@
         <v>-5.747944872191722</v>
       </c>
       <c r="E25">
-        <v>-30.13578975943079</v>
+        <v>-30.47564041252143</v>
       </c>
       <c r="F25">
-        <v>0.7336956301882508</v>
+        <v>0.05023785063007386</v>
       </c>
       <c r="G25">
-        <v>-9.250497463120885</v>
+        <v>-7.094941615523952</v>
       </c>
     </row>
     <row r="26" spans="1:7">
@@ -978,13 +978,13 @@
         <v>-5.220628348481363</v>
       </c>
       <c r="E26">
-        <v>-29.71976338082012</v>
+        <v>-31.71140889176358</v>
       </c>
       <c r="F26">
-        <v>1.091909859650452</v>
+        <v>0.4325277502872401</v>
       </c>
       <c r="G26">
-        <v>-9.662549985334394</v>
+        <v>-7.44004737426011</v>
       </c>
     </row>
     <row r="27" spans="1:7">
@@ -1001,13 +1001,13 @@
         <v>-4.723541424081758</v>
       </c>
       <c r="E27">
-        <v>-28.86906010339819</v>
+        <v>-30.62052440992283</v>
       </c>
       <c r="F27">
-        <v>0.6573574321832624</v>
+        <v>0.4559630924798409</v>
       </c>
       <c r="G27">
-        <v>-8.27588934820526</v>
+        <v>-8.354517260434234</v>
       </c>
     </row>
     <row r="28" spans="1:7">
@@ -1024,13 +1024,13 @@
         <v>-4.264077399316032</v>
       </c>
       <c r="E28">
-        <v>-29.72965809652688</v>
+        <v>-30.72851719382075</v>
       </c>
       <c r="F28">
-        <v>0.6087952215615441</v>
+        <v>-0.01548316237323331</v>
       </c>
       <c r="G28">
-        <v>-9.081927986725972</v>
+        <v>-8.184136549738506</v>
       </c>
     </row>
     <row r="29" spans="1:7">
@@ -1047,13 +1047,13 @@
         <v>-3.84830830602985</v>
       </c>
       <c r="E29">
-        <v>-28.52714673039706</v>
+        <v>-30.36410862618651</v>
       </c>
       <c r="F29">
-        <v>0.5951511820700335</v>
+        <v>0.08588912691175898</v>
       </c>
       <c r="G29">
-        <v>-9.50810616775289</v>
+        <v>-8.129835614151256</v>
       </c>
     </row>
     <row r="30" spans="1:7">
@@ -1070,13 +1070,13 @@
         <v>-3.478772094782726</v>
       </c>
       <c r="E30">
-        <v>-28.64230129593811</v>
+        <v>-29.57518052694022</v>
       </c>
       <c r="F30">
-        <v>0.163621467255659</v>
+        <v>-0.5302016736137481</v>
       </c>
       <c r="G30">
-        <v>-9.189575022426675</v>
+        <v>-8.391470377636699</v>
       </c>
     </row>
     <row r="31" spans="1:7">
@@ -1093,13 +1093,13 @@
         <v>-3.146488540467604</v>
       </c>
       <c r="E31">
-        <v>-28.65468214387508</v>
+        <v>-29.9380788484929</v>
       </c>
       <c r="F31">
-        <v>0.4126610148658996</v>
+        <v>-0.2379221759447762</v>
       </c>
       <c r="G31">
-        <v>-8.772672854748308</v>
+        <v>-7.657927048250357</v>
       </c>
     </row>
     <row r="32" spans="1:7">
@@ -1116,13 +1116,13 @@
         <v>-2.850490368991452</v>
       </c>
       <c r="E32">
-        <v>-26.938385966494</v>
+        <v>-29.08904884221681</v>
       </c>
       <c r="F32">
-        <v>-0.05988199842848121</v>
+        <v>-0.1763603956709253</v>
       </c>
       <c r="G32">
-        <v>-8.571543816819025</v>
+        <v>-7.618647544962244</v>
       </c>
     </row>
     <row r="33" spans="1:7">
@@ -1139,13 +1139,13 @@
         <v>-2.582686873562465</v>
       </c>
       <c r="E33">
-        <v>-28.17699606317597</v>
+        <v>-29.91136990879566</v>
       </c>
       <c r="F33">
-        <v>0.2410928718676772</v>
+        <v>-0.4219141732501855</v>
       </c>
       <c r="G33">
-        <v>-9.034061526616792</v>
+        <v>-7.293301302457063</v>
       </c>
     </row>
     <row r="34" spans="1:7">
@@ -1162,13 +1162,13 @@
         <v>-2.337223895362376</v>
       </c>
       <c r="E34">
-        <v>-27.9377296105067</v>
+        <v>-27.51050884414907</v>
       </c>
       <c r="F34">
-        <v>0.06607126516718362</v>
+        <v>-0.6626319419319023</v>
       </c>
       <c r="G34">
-        <v>-8.250154727514534</v>
+        <v>-6.954295334599914</v>
       </c>
     </row>
     <row r="35" spans="1:7">
@@ -1185,13 +1185,13 @@
         <v>-2.115651113748188</v>
       </c>
       <c r="E35">
-        <v>-27.76678877366516</v>
+        <v>-29.00900353565723</v>
       </c>
       <c r="F35">
-        <v>-0.002011423301504952</v>
+        <v>-1.396146306906448</v>
       </c>
       <c r="G35">
-        <v>-8.509308887501037</v>
+        <v>-7.99059369605466</v>
       </c>
     </row>
     <row r="36" spans="1:7">
@@ -1208,13 +1208,13 @@
         <v>-1.917192375866624</v>
       </c>
       <c r="E36">
-        <v>-26.67132374036565</v>
+        <v>-27.63442600689496</v>
       </c>
       <c r="F36">
-        <v>-0.1520768052578578</v>
+        <v>-0.6577818507885111</v>
       </c>
       <c r="G36">
-        <v>-8.36433795656165</v>
+        <v>-7.262247821618478</v>
       </c>
     </row>
     <row r="37" spans="1:7">
@@ -1231,13 +1231,13 @@
         <v>-1.748363021224418</v>
       </c>
       <c r="E37">
-        <v>-25.92890759765214</v>
+        <v>-29.71636476107736</v>
       </c>
       <c r="F37">
-        <v>-0.3521739216084951</v>
+        <v>-0.4153211970913043</v>
       </c>
       <c r="G37">
-        <v>-8.431970495344926</v>
+        <v>-8.115034023696602</v>
       </c>
     </row>
     <row r="38" spans="1:7">
@@ -1254,13 +1254,13 @@
         <v>-1.617234438290117</v>
       </c>
       <c r="E38">
-        <v>-25.38192227921366</v>
+        <v>-27.18963928986158</v>
       </c>
       <c r="F38">
-        <v>-0.5317382951459412</v>
+        <v>-1.073928782932899</v>
       </c>
       <c r="G38">
-        <v>-8.410695054753486</v>
+        <v>-7.377126669636198</v>
       </c>
     </row>
     <row r="39" spans="1:7">
@@ -1277,13 +1277,13 @@
         <v>-1.528573019387621</v>
       </c>
       <c r="E39">
-        <v>-25.61493490927834</v>
+        <v>-26.77847649233515</v>
       </c>
       <c r="F39">
-        <v>-0.2865208347322176</v>
+        <v>-0.773815414735652</v>
       </c>
       <c r="G39">
-        <v>-8.058390295915906</v>
+        <v>-7.086492470008382</v>
       </c>
     </row>
     <row r="40" spans="1:7">
@@ -1300,13 +1300,13 @@
         <v>-1.489462969438038</v>
       </c>
       <c r="E40">
-        <v>-24.82629210389453</v>
+        <v>-25.56648476587027</v>
       </c>
       <c r="F40">
-        <v>-0.2028408164362171</v>
+        <v>-0.4543671229896618</v>
       </c>
       <c r="G40">
-        <v>-8.480900071239365</v>
+        <v>-6.882915640795753</v>
       </c>
     </row>
     <row r="41" spans="1:7">
@@ -1323,13 +1323,13 @@
         <v>-1.502906784017272</v>
       </c>
       <c r="E41">
-        <v>-25.21157467246712</v>
+        <v>-24.28009926840738</v>
       </c>
       <c r="F41">
-        <v>-0.452965525344125</v>
+        <v>-0.5472453329263479</v>
       </c>
       <c r="G41">
-        <v>-8.259706363474077</v>
+        <v>-7.762374892930602</v>
       </c>
     </row>
     <row r="42" spans="1:7">
@@ -1346,13 +1346,13 @@
         <v>-1.568394897708433</v>
       </c>
       <c r="E42">
-        <v>-23.90478839959968</v>
+        <v>-23.65503852960265</v>
       </c>
       <c r="F42">
-        <v>-0.537841706169768</v>
+        <v>-1.116631122547213</v>
       </c>
       <c r="G42">
-        <v>-8.405691191875333</v>
+        <v>-7.944718937432063</v>
       </c>
     </row>
     <row r="43" spans="1:7">
@@ -1369,13 +1369,13 @@
         <v>-1.685448215127747</v>
       </c>
       <c r="E43">
-        <v>-22.29214446378017</v>
+        <v>-23.80672882343758</v>
       </c>
       <c r="F43">
-        <v>-0.2967793366484866</v>
+        <v>-1.302776875099901</v>
       </c>
       <c r="G43">
-        <v>-8.082937114402112</v>
+        <v>-7.930619528391129</v>
       </c>
     </row>
     <row r="44" spans="1:7">
@@ -1392,13 +1392,13 @@
         <v>-1.848998935607228</v>
       </c>
       <c r="E44">
-        <v>-21.80162921621733</v>
+        <v>-22.05883295443099</v>
       </c>
       <c r="F44">
-        <v>-0.3643881989627739</v>
+        <v>-1.213605609290743</v>
       </c>
       <c r="G44">
-        <v>-8.862703011896352</v>
+        <v>-8.264677414136637</v>
       </c>
     </row>
     <row r="45" spans="1:7">
@@ -1415,13 +1415,13 @@
         <v>-2.051527406240828</v>
       </c>
       <c r="E45">
-        <v>-21.84574108152605</v>
+        <v>-23.6265544280944</v>
       </c>
       <c r="F45">
-        <v>-0.3059468786952688</v>
+        <v>-0.961989839057796</v>
       </c>
       <c r="G45">
-        <v>-8.518122248609705</v>
+        <v>-8.146169535074172</v>
       </c>
     </row>
     <row r="46" spans="1:7">
@@ -1438,13 +1438,13 @@
         <v>-2.287476362199831</v>
       </c>
       <c r="E46">
-        <v>-21.28793723868324</v>
+        <v>-23.56793333206511</v>
       </c>
       <c r="F46">
-        <v>-0.2889786008163237</v>
+        <v>-1.080670036856881</v>
       </c>
       <c r="G46">
-        <v>-8.830888287655975</v>
+        <v>-8.409038037865967</v>
       </c>
     </row>
     <row r="47" spans="1:7">
@@ -1461,13 +1461,13 @@
         <v>-2.547001043338275</v>
       </c>
       <c r="E47">
-        <v>-20.93168671697382</v>
+        <v>-22.88223179782366</v>
       </c>
       <c r="F47">
-        <v>-0.5914627565203827</v>
+        <v>-0.5175036296962345</v>
       </c>
       <c r="G47">
-        <v>-9.042638639773182</v>
+        <v>-8.400296863631606</v>
       </c>
     </row>
     <row r="48" spans="1:7">
@@ -1484,13 +1484,13 @@
         <v>-2.822917269870094</v>
       </c>
       <c r="E48">
-        <v>-20.18645839190155</v>
+        <v>-22.16302861287348</v>
       </c>
       <c r="F48">
-        <v>-0.5968985034175531</v>
+        <v>-0.7779025795010647</v>
       </c>
       <c r="G48">
-        <v>-8.181436104395084</v>
+        <v>-8.919451738766949</v>
       </c>
     </row>
     <row r="49" spans="1:7">
@@ -1507,13 +1507,13 @@
         <v>-3.110428765980611</v>
       </c>
       <c r="E49">
-        <v>-19.00271981477052</v>
+        <v>-22.13698535885536</v>
       </c>
       <c r="F49">
-        <v>-0.7849867775298061</v>
+        <v>-0.7672887079689946</v>
       </c>
       <c r="G49">
-        <v>-9.227076103629569</v>
+        <v>-7.518432476093684</v>
       </c>
     </row>
     <row r="50" spans="1:7">
@@ -1530,13 +1530,13 @@
         <v>-3.400291919068174</v>
       </c>
       <c r="E50">
-        <v>-18.84792751624034</v>
+        <v>-19.24574490086616</v>
       </c>
       <c r="F50">
-        <v>-0.6819884030331184</v>
+        <v>-0.985536182482372</v>
       </c>
       <c r="G50">
-        <v>-9.551037670636665</v>
+        <v>-8.101558046751961</v>
       </c>
     </row>
     <row r="51" spans="1:7">
@@ -1553,13 +1553,13 @@
         <v>-3.692296187071202</v>
       </c>
       <c r="E51">
-        <v>-18.4364069692673</v>
+        <v>-18.46258154903163</v>
       </c>
       <c r="F51">
-        <v>-0.4120143544193287</v>
+        <v>-1.145899827990328</v>
       </c>
       <c r="G51">
-        <v>-8.622996652092677</v>
+        <v>-7.141758084734109</v>
       </c>
     </row>
     <row r="52" spans="1:7">
@@ -1576,13 +1576,13 @@
         <v>-3.981840904920156</v>
       </c>
       <c r="E52">
-        <v>-17.24074944854809</v>
+        <v>-19.02255453092412</v>
       </c>
       <c r="F52">
-        <v>-0.6737005871681093</v>
+        <v>-0.4706147212281713</v>
       </c>
       <c r="G52">
-        <v>-8.888903566048517</v>
+        <v>-8.539968621752489</v>
       </c>
     </row>
     <row r="53" spans="1:7">
@@ -1599,13 +1599,13 @@
         <v>-4.265186043064381</v>
       </c>
       <c r="E53">
-        <v>-16.19118049931632</v>
+        <v>-18.26651673839554</v>
       </c>
       <c r="F53">
-        <v>-0.211323298640884</v>
+        <v>-1.125039051685628</v>
       </c>
       <c r="G53">
-        <v>-9.113063498103543</v>
+        <v>-8.378181430320948</v>
       </c>
     </row>
     <row r="54" spans="1:7">
@@ -1622,13 +1622,13 @@
         <v>-4.543431392834372</v>
       </c>
       <c r="E54">
-        <v>-16.65220632414121</v>
+        <v>-19.09439877105581</v>
       </c>
       <c r="F54">
-        <v>-0.295542584116107</v>
+        <v>-0.8947305477874902</v>
       </c>
       <c r="G54">
-        <v>-9.292296944566651</v>
+        <v>-8.669770465422562</v>
       </c>
     </row>
     <row r="55" spans="1:7">
@@ -1645,13 +1645,13 @@
         <v>-4.811244709639524</v>
       </c>
       <c r="E55">
-        <v>-15.10463655981193</v>
+        <v>-18.03717670075108</v>
       </c>
       <c r="F55">
-        <v>-0.440165592236067</v>
+        <v>-0.6342794108362836</v>
       </c>
       <c r="G55">
-        <v>-8.693674164483117</v>
+        <v>-8.834865128186022</v>
       </c>
     </row>
     <row r="56" spans="1:7">
@@ -1668,13 +1668,13 @@
         <v>-5.069863635341619</v>
       </c>
       <c r="E56">
-        <v>-15.30990322963161</v>
+        <v>-16.61983679193438</v>
       </c>
       <c r="F56">
-        <v>-0.9182106218198421</v>
+        <v>-1.01916127209681</v>
       </c>
       <c r="G56">
-        <v>-9.90093729407117</v>
+        <v>-8.243572597066288</v>
       </c>
     </row>
     <row r="57" spans="1:7">
@@ -1691,13 +1691,13 @@
         <v>-5.317064872955302</v>
       </c>
       <c r="E57">
-        <v>-15.46725864445014</v>
+        <v>-16.41446596721252</v>
       </c>
       <c r="F57">
-        <v>-0.0790148003309414</v>
+        <v>-0.7162869553460318</v>
       </c>
       <c r="G57">
-        <v>-9.643020154612579</v>
+        <v>-8.659047433366297</v>
       </c>
     </row>
     <row r="58" spans="1:7">
@@ -1714,13 +1714,13 @@
         <v>-5.548598436711342</v>
       </c>
       <c r="E58">
-        <v>-13.77037150666594</v>
+        <v>-16.20330322423485</v>
       </c>
       <c r="F58">
-        <v>-0.5823242073326986</v>
+        <v>-0.7985753164053292</v>
       </c>
       <c r="G58">
-        <v>-9.251140582546537</v>
+        <v>-9.299331883590101</v>
       </c>
     </row>
     <row r="59" spans="1:7">
@@ -1737,13 +1737,13 @@
         <v>-5.76489037335067</v>
       </c>
       <c r="E59">
-        <v>-13.71119793680771</v>
+        <v>-16.96414119921157</v>
       </c>
       <c r="F59">
-        <v>-0.5666051074971752</v>
+        <v>-1.06736894147013</v>
       </c>
       <c r="G59">
-        <v>-9.569186107081954</v>
+        <v>-9.653260847099606</v>
       </c>
     </row>
     <row r="60" spans="1:7">
@@ -1760,13 +1760,13 @@
         <v>-5.960460128640994</v>
       </c>
       <c r="E60">
-        <v>-13.61701020592218</v>
+        <v>-16.39965332873343</v>
       </c>
       <c r="F60">
-        <v>-0.7102448435100123</v>
+        <v>-0.9006981065572578</v>
       </c>
       <c r="G60">
-        <v>-10.02619136465985</v>
+        <v>-9.320597480516863</v>
       </c>
     </row>
     <row r="61" spans="1:7">
@@ -1783,13 +1783,13 @@
         <v>-6.133880679752385</v>
       </c>
       <c r="E61">
-        <v>-13.09012225512973</v>
+        <v>-14.90775662385445</v>
       </c>
       <c r="F61">
-        <v>-0.7129983367569178</v>
+        <v>-1.253615754845959</v>
       </c>
       <c r="G61">
-        <v>-9.753469353525047</v>
+        <v>-9.221786774475744</v>
       </c>
     </row>
     <row r="62" spans="1:7">
@@ -1806,13 +1806,13 @@
         <v>-6.282073865192704</v>
       </c>
       <c r="E62">
-        <v>-12.49659328084041</v>
+        <v>-14.76533611631322</v>
       </c>
       <c r="F62">
-        <v>-0.9616402680138146</v>
+        <v>-0.8528872251698787</v>
       </c>
       <c r="G62">
-        <v>-9.548222382538661</v>
+        <v>-9.194185138717694</v>
       </c>
     </row>
     <row r="63" spans="1:7">
@@ -1829,13 +1829,13 @@
         <v>-6.399287933640943</v>
       </c>
       <c r="E63">
-        <v>-11.54397443163885</v>
+        <v>-14.02604009219099</v>
       </c>
       <c r="F63">
-        <v>-0.8631830036192738</v>
+        <v>-0.9146188207613035</v>
       </c>
       <c r="G63">
-        <v>-9.660551721404691</v>
+        <v>-9.809653710287419</v>
       </c>
     </row>
     <row r="64" spans="1:7">
@@ -1852,13 +1852,13 @@
         <v>-6.48432807745643</v>
       </c>
       <c r="E64">
-        <v>-11.9684283003778</v>
+        <v>-14.35253401119601</v>
       </c>
       <c r="F64">
-        <v>-0.6010171461442723</v>
+        <v>-1.06196881437128</v>
       </c>
       <c r="G64">
-        <v>-9.806438113159162</v>
+        <v>-10.61963309590102</v>
       </c>
     </row>
     <row r="65" spans="1:7">
@@ -1875,13 +1875,13 @@
         <v>-6.530853369755825</v>
       </c>
       <c r="E65">
-        <v>-11.10473509526487</v>
+        <v>-14.24247397891359</v>
       </c>
       <c r="F65">
-        <v>-1.034940014385334</v>
+        <v>-1.894804430941486</v>
       </c>
       <c r="G65">
-        <v>-10.32580298647431</v>
+        <v>-10.72215158230432</v>
       </c>
     </row>
     <row r="66" spans="1:7">
@@ -1898,13 +1898,13 @@
         <v>-6.536815238917142</v>
       </c>
       <c r="E66">
-        <v>-10.22333555678195</v>
+        <v>-12.76653561643764</v>
       </c>
       <c r="F66">
-        <v>-1.19192723435948</v>
+        <v>-1.339449528389238</v>
       </c>
       <c r="G66">
-        <v>-9.143129331252736</v>
+        <v>-10.06843381101615</v>
       </c>
     </row>
     <row r="67" spans="1:7">
@@ -1921,13 +1921,13 @@
         <v>-6.499470899433557</v>
       </c>
       <c r="E67">
-        <v>-11.14817221794644</v>
+        <v>-12.66714466891729</v>
       </c>
       <c r="F67">
-        <v>-1.004778328882002</v>
+        <v>-1.432172005254198</v>
       </c>
       <c r="G67">
-        <v>-10.21981953010425</v>
+        <v>-9.931570778550146</v>
       </c>
     </row>
     <row r="68" spans="1:7">
@@ -1944,13 +1944,13 @@
         <v>-6.417073043567608</v>
       </c>
       <c r="E68">
-        <v>-11.04025415386965</v>
+        <v>-12.88190754873105</v>
       </c>
       <c r="F68">
-        <v>-1.513973286280649</v>
+        <v>-1.399175646498485</v>
       </c>
       <c r="G68">
-        <v>-9.356287327418942</v>
+        <v>-10.66047774187299</v>
       </c>
     </row>
     <row r="69" spans="1:7">
@@ -1967,13 +1967,13 @@
         <v>-6.292486014573142</v>
       </c>
       <c r="E69">
-        <v>-11.82747048994104</v>
+        <v>-13.00440277063854</v>
       </c>
       <c r="F69">
-        <v>-1.187118561586229</v>
+        <v>-1.535382441806003</v>
       </c>
       <c r="G69">
-        <v>-9.60613594306286</v>
+        <v>-9.169612070459014</v>
       </c>
     </row>
     <row r="70" spans="1:7">
@@ -1990,13 +1990,13 @@
         <v>-6.123998441963439</v>
       </c>
       <c r="E70">
-        <v>-10.4975980565825</v>
+        <v>-13.46938195327212</v>
       </c>
       <c r="F70">
-        <v>-1.31115332627701</v>
+        <v>-1.495624119941237</v>
       </c>
       <c r="G70">
-        <v>-9.132521141951051</v>
+        <v>-9.678509846999532</v>
       </c>
     </row>
     <row r="71" spans="1:7">
@@ -2013,13 +2013,13 @@
         <v>-5.91730676870709</v>
       </c>
       <c r="E71">
-        <v>-10.66328586357514</v>
+        <v>-13.67978844109051</v>
       </c>
       <c r="F71">
-        <v>-1.774556133648901</v>
+        <v>-1.702070672434333</v>
       </c>
       <c r="G71">
-        <v>-8.693444478973955</v>
+        <v>-10.39882657227975</v>
       </c>
     </row>
     <row r="72" spans="1:7">
@@ -2036,13 +2036,13 @@
         <v>-5.673778837708968</v>
       </c>
       <c r="E72">
-        <v>-11.03398674584303</v>
+        <v>-13.11034642004799</v>
       </c>
       <c r="F72">
-        <v>-1.817587335122127</v>
+        <v>-1.784418675946632</v>
       </c>
       <c r="G72">
-        <v>-8.835639496474052</v>
+        <v>-8.297817751887028</v>
       </c>
     </row>
     <row r="73" spans="1:7">
@@ -2059,13 +2059,13 @@
         <v>-5.396290547959639</v>
       </c>
       <c r="E73">
-        <v>-11.56637226408079</v>
+        <v>-12.82288341851508</v>
       </c>
       <c r="F73">
-        <v>-1.890948380681454</v>
+        <v>-1.784430273090271</v>
       </c>
       <c r="G73">
-        <v>-9.036745565852419</v>
+        <v>-10.27787090193394</v>
       </c>
     </row>
     <row r="74" spans="1:7">
@@ -2082,13 +2082,13 @@
         <v>-5.090351837851182</v>
       </c>
       <c r="E74">
-        <v>-10.54245712010248</v>
+        <v>-13.04652210738388</v>
       </c>
       <c r="F74">
-        <v>-2.082646679935107</v>
+        <v>-2.310402155497817</v>
       </c>
       <c r="G74">
-        <v>-8.711612602748602</v>
+        <v>-8.045921653990018</v>
       </c>
     </row>
     <row r="75" spans="1:7">
@@ -2105,13 +2105,13 @@
         <v>-4.755742684977307</v>
       </c>
       <c r="E75">
-        <v>-10.76956914853516</v>
+        <v>-12.33320141016965</v>
       </c>
       <c r="F75">
-        <v>-2.028387786684337</v>
+        <v>-1.868146739551995</v>
       </c>
       <c r="G75">
-        <v>-8.359511279647707</v>
+        <v>-8.631275174087158</v>
       </c>
     </row>
     <row r="76" spans="1:7">
@@ -2128,13 +2128,13 @@
         <v>-4.400811525986788</v>
       </c>
       <c r="E76">
-        <v>-11.95222089190434</v>
+        <v>-14.10331850113189</v>
       </c>
       <c r="F76">
-        <v>-1.868002603623908</v>
+        <v>-2.598350948384954</v>
       </c>
       <c r="G76">
-        <v>-7.739606496529615</v>
+        <v>-7.45292945010249</v>
       </c>
     </row>
     <row r="77" spans="1:7">
@@ -2151,13 +2151,13 @@
         <v>-4.02831344047572</v>
       </c>
       <c r="E77">
-        <v>-11.07277765419274</v>
+        <v>-14.63358922200806</v>
       </c>
       <c r="F77">
-        <v>-2.111398484118875</v>
+        <v>-2.325095736488675</v>
       </c>
       <c r="G77">
-        <v>-7.906719110552134</v>
+        <v>-7.326028206290965</v>
       </c>
     </row>
     <row r="78" spans="1:7">
@@ -2174,13 +2174,13 @@
         <v>-3.640833097219013</v>
       </c>
       <c r="E78">
-        <v>-11.34543707419457</v>
+        <v>-13.62045637464201</v>
       </c>
       <c r="F78">
-        <v>-2.22427016968953</v>
+        <v>-2.320239018406062</v>
       </c>
       <c r="G78">
-        <v>-7.035118384052156</v>
+        <v>-7.583820659330298</v>
       </c>
     </row>
     <row r="79" spans="1:7">
@@ -2197,13 +2197,13 @@
         <v>-3.245286825681329</v>
       </c>
       <c r="E79">
-        <v>-12.26784194481695</v>
+        <v>-14.68335715135236</v>
       </c>
       <c r="F79">
-        <v>-2.37720170285957</v>
+        <v>-2.917419019493058</v>
       </c>
       <c r="G79">
-        <v>-6.645260044466732</v>
+        <v>-7.961295668750378</v>
       </c>
     </row>
     <row r="80" spans="1:7">
@@ -2220,13 +2220,13 @@
         <v>-2.840283347784536</v>
       </c>
       <c r="E80">
-        <v>-13.2476769228046</v>
+        <v>-15.05832385613548</v>
       </c>
       <c r="F80">
-        <v>-2.769324323587966</v>
+        <v>-2.138873774134929</v>
       </c>
       <c r="G80">
-        <v>-6.30987326398965</v>
+        <v>-6.879539263811084</v>
       </c>
     </row>
     <row r="81" spans="1:7">
@@ -2243,13 +2243,13 @@
         <v>-2.432572484963802</v>
       </c>
       <c r="E81">
-        <v>-13.26142084141788</v>
+        <v>-17.00593901430236</v>
       </c>
       <c r="F81">
-        <v>-2.240975855101788</v>
+        <v>-2.729176669043885</v>
       </c>
       <c r="G81">
-        <v>-5.847828050096442</v>
+        <v>-5.853442220184652</v>
       </c>
     </row>
     <row r="82" spans="1:7">
@@ -2266,13 +2266,13 @@
         <v>-2.024913982311856</v>
       </c>
       <c r="E82">
-        <v>-14.35029694503622</v>
+        <v>-15.62849948996725</v>
       </c>
       <c r="F82">
-        <v>-2.671683829452585</v>
+        <v>-2.434575257544866</v>
       </c>
       <c r="G82">
-        <v>-5.363253968976087</v>
+        <v>-6.295301359044156</v>
       </c>
     </row>
     <row r="83" spans="1:7">
@@ -2289,13 +2289,13 @@
         <v>-1.617732702064525</v>
       </c>
       <c r="E83">
-        <v>-14.66166123238161</v>
+        <v>-18.15233126629213</v>
       </c>
       <c r="F83">
-        <v>-2.410145874468906</v>
+        <v>-2.378682823775775</v>
       </c>
       <c r="G83">
-        <v>-5.196968222786547</v>
+        <v>-4.471946225790084</v>
       </c>
     </row>
     <row r="84" spans="1:7">
@@ -2312,13 +2312,13 @@
         <v>-1.219961825103035</v>
       </c>
       <c r="E84">
-        <v>-15.59165129696683</v>
+        <v>-18.10356865817754</v>
       </c>
       <c r="F84">
-        <v>-2.752591302051416</v>
+        <v>-2.988480517142214</v>
       </c>
       <c r="G84">
-        <v>-5.196594163528771</v>
+        <v>-6.227734444692071</v>
       </c>
     </row>
     <row r="85" spans="1:7">
@@ -2335,13 +2335,13 @@
         <v>-0.8320902739203255</v>
       </c>
       <c r="E85">
-        <v>-15.99916414444308</v>
+        <v>-19.49279580035462</v>
       </c>
       <c r="F85">
-        <v>-2.893663099115575</v>
+        <v>-2.931780425155393</v>
       </c>
       <c r="G85">
-        <v>-4.635794024360956</v>
+        <v>-5.329076765212911</v>
       </c>
     </row>
     <row r="86" spans="1:7">
@@ -2358,13 +2358,13 @@
         <v>-0.4611084230987575</v>
       </c>
       <c r="E86">
-        <v>-18.0546067972066</v>
+        <v>-19.48683632856052</v>
       </c>
       <c r="F86">
-        <v>-3.143222861454773</v>
+        <v>-3.740233047224196</v>
       </c>
       <c r="G86">
-        <v>-4.879237695520838</v>
+        <v>-4.526394816347509</v>
       </c>
     </row>
     <row r="87" spans="1:7">
@@ -2381,13 +2381,13 @@
         <v>-0.1137575763041174</v>
       </c>
       <c r="E87">
-        <v>-17.98105079390001</v>
+        <v>-21.09919497051755</v>
       </c>
       <c r="F87">
-        <v>-3.431241237203744</v>
+        <v>-3.189343873340441</v>
       </c>
       <c r="G87">
-        <v>-4.962059008902782</v>
+        <v>-6.090307042117847</v>
       </c>
     </row>
     <row r="88" spans="1:7">
@@ -2404,13 +2404,13 @@
         <v>0.2068799501308304</v>
       </c>
       <c r="E88">
-        <v>-19.65528197622384</v>
+        <v>-23.90386459090211</v>
       </c>
       <c r="F88">
-        <v>-3.570096323098011</v>
+        <v>-2.959038682911914</v>
       </c>
       <c r="G88">
-        <v>-4.615749041854309</v>
+        <v>-4.969730504908764</v>
       </c>
     </row>
     <row r="89" spans="1:7">
@@ -2427,13 +2427,13 @@
         <v>0.4909688176678991</v>
       </c>
       <c r="E89">
-        <v>-21.05492913709257</v>
+        <v>-23.94727454273964</v>
       </c>
       <c r="F89">
-        <v>-3.319951733372436</v>
+        <v>-3.383384795609211</v>
       </c>
       <c r="G89">
-        <v>-3.824659648758425</v>
+        <v>-4.628417838295324</v>
       </c>
     </row>
     <row r="90" spans="1:7">
@@ -2450,13 +2450,13 @@
         <v>0.7350355134518664</v>
       </c>
       <c r="E90">
-        <v>-23.55236443842674</v>
+        <v>-24.09518356077817</v>
       </c>
       <c r="F90">
-        <v>-4.023199210183494</v>
+        <v>-3.399698663239945</v>
       </c>
       <c r="G90">
-        <v>-4.847272035088728</v>
+        <v>-4.894275533927773</v>
       </c>
     </row>
     <row r="91" spans="1:7">
@@ -2473,13 +2473,13 @@
         <v>0.9341836583867816</v>
       </c>
       <c r="E91">
-        <v>-23.68168407066378</v>
+        <v>-25.74611121585852</v>
       </c>
       <c r="F91">
-        <v>-4.084615197794451</v>
+        <v>-3.714869265717878</v>
       </c>
       <c r="G91">
-        <v>-4.270643283118151</v>
+        <v>-4.813331079277831</v>
       </c>
     </row>
     <row r="92" spans="1:7">
@@ -2496,13 +2496,13 @@
         <v>1.082723315017241</v>
       </c>
       <c r="E92">
-        <v>-26.07648603708811</v>
+        <v>-28.80927518954893</v>
       </c>
       <c r="F92">
-        <v>-3.968453236899877</v>
+        <v>-4.331217688505656</v>
       </c>
       <c r="G92">
-        <v>-4.549537272006273</v>
+        <v>-5.740597729533789</v>
       </c>
     </row>
     <row r="93" spans="1:7">
@@ -2519,13 +2519,13 @@
         <v>1.178038683164059</v>
       </c>
       <c r="E93">
-        <v>-26.65530652780052</v>
+        <v>-29.14779220704431</v>
       </c>
       <c r="F93">
-        <v>-4.469921183165211</v>
+        <v>-3.962576798544417</v>
       </c>
       <c r="G93">
-        <v>-4.519310659000668</v>
+        <v>-5.190241718589686</v>
       </c>
     </row>
     <row r="94" spans="1:7">
@@ -2542,13 +2542,13 @@
         <v>1.215852071981</v>
       </c>
       <c r="E94">
-        <v>-28.80774909380834</v>
+        <v>-31.41167146143288</v>
       </c>
       <c r="F94">
-        <v>-4.395003635256024</v>
+        <v>-4.068540728343127</v>
       </c>
       <c r="G94">
-        <v>-5.118005625958511</v>
+        <v>-5.790544484111656</v>
       </c>
     </row>
     <row r="95" spans="1:7">
@@ -2565,13 +2565,13 @@
         <v>1.195823351706607</v>
       </c>
       <c r="E95">
-        <v>-31.2946081440976</v>
+        <v>-33.10527545556152</v>
       </c>
       <c r="F95">
-        <v>-4.342867847658629</v>
+        <v>-4.450497624304368</v>
       </c>
       <c r="G95">
-        <v>-4.908657128022819</v>
+        <v>-5.865441647427541</v>
       </c>
     </row>
     <row r="96" spans="1:7">
@@ -2588,13 +2588,13 @@
         <v>1.116100445507769</v>
       </c>
       <c r="E96">
-        <v>-33.07322291653523</v>
+        <v>-35.39564175442096</v>
       </c>
       <c r="F96">
-        <v>-4.595397307136863</v>
+        <v>-5.003225773822338</v>
       </c>
       <c r="G96">
-        <v>-4.630419383446585</v>
+        <v>-5.85073521239811</v>
       </c>
     </row>
     <row r="97" spans="1:7">
@@ -2611,13 +2611,13 @@
         <v>0.9834415198107229</v>
       </c>
       <c r="E97">
-        <v>-35.90286254259809</v>
+        <v>-36.62863427909641</v>
       </c>
       <c r="F97">
-        <v>-4.682066903389567</v>
+        <v>-4.603513650949493</v>
       </c>
       <c r="G97">
-        <v>-4.84784296764007</v>
+        <v>-5.726957691511177</v>
       </c>
     </row>
     <row r="98" spans="1:7">
@@ -2634,13 +2634,13 @@
         <v>0.7949820294854373</v>
       </c>
       <c r="E98">
-        <v>-37.00159034142012</v>
+        <v>-39.19819911442475</v>
       </c>
       <c r="F98">
-        <v>-5.238768731338767</v>
+        <v>-4.585147917262025</v>
       </c>
       <c r="G98">
-        <v>-6.122896134646252</v>
+        <v>-6.452806556340621</v>
       </c>
     </row>
     <row r="99" spans="1:7">
@@ -2657,13 +2657,13 @@
         <v>0.5707114441721343</v>
       </c>
       <c r="E99">
-        <v>-39.03311585871213</v>
+        <v>-41.5270031006613</v>
       </c>
       <c r="F99">
-        <v>-5.871051629486796</v>
+        <v>-5.135284105176635</v>
       </c>
       <c r="G99">
-        <v>-6.357152385439689</v>
+        <v>-7.54073822025479</v>
       </c>
     </row>
     <row r="100" spans="1:7">
@@ -2680,13 +2680,13 @@
         <v>0.2998687041795047</v>
       </c>
       <c r="E100">
-        <v>-42.30089893043912</v>
+        <v>-44.6192127066369</v>
       </c>
       <c r="F100">
-        <v>-5.748951931048954</v>
+        <v>-4.781031957002024</v>
       </c>
       <c r="G100">
-        <v>-6.731566015144806</v>
+        <v>-8.525022657549219</v>
       </c>
     </row>
     <row r="101" spans="1:7">
@@ -2703,13 +2703,13 @@
         <v>0.02337321046350054</v>
       </c>
       <c r="E101">
-        <v>-43.45806895056715</v>
+        <v>-45.21259224128397</v>
       </c>
       <c r="F101">
-        <v>-5.263559282602347</v>
+        <v>-5.426000473556525</v>
       </c>
       <c r="G101">
-        <v>-7.510144110434527</v>
+        <v>-7.743012404508319</v>
       </c>
     </row>
     <row r="102" spans="1:7">
@@ -2726,13 +2726,13 @@
         <v>-0.3020397386828146</v>
       </c>
       <c r="E102">
-        <v>-45.85712768255868</v>
+        <v>-48.19321798347357</v>
       </c>
       <c r="F102">
-        <v>-5.517061245411469</v>
+        <v>-4.701615545728233</v>
       </c>
       <c r="G102">
-        <v>-8.33237229612954</v>
+        <v>-8.929383996427388</v>
       </c>
     </row>
   </sheetData>
